--- a/Feuilles/OVLM.xlsx
+++ b/Feuilles/OVLM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F2442F1-CAE1-D84B-99ED-2EC92426B5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BF263C-DB8A-8E4C-AA57-E82E41522574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="5460" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
+    <workbookView xWindow="1280" yWindow="4160" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>MES</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>COUPLET 4</t>
+  </si>
+  <si>
+    <t>LOOP</t>
   </si>
 </sst>
 </file>
@@ -458,10 +461,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B34C31-2D9C-7940-9F39-E67ACD52E89F}">
-  <dimension ref="A1:D224"/>
+  <dimension ref="A1:E224"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -474,8 +477,11 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -489,7 +495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -500,7 +506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -511,7 +517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -522,7 +528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -533,7 +539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -544,7 +550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -555,7 +561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -566,7 +572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -580,7 +586,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -591,7 +597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -602,7 +608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -613,7 +619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -624,7 +630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -635,7 +641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>

--- a/Feuilles/OVLM.xlsx
+++ b/Feuilles/OVLM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanaismusic/Documents/CLIC/Feuilles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BF263C-DB8A-8E4C-AA57-E82E41522574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71A0780-47C4-DC46-BE39-4B86B0BB8A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1280" yWindow="4160" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
+    <workbookView xWindow="20800" yWindow="2040" windowWidth="28040" windowHeight="17440" xr2:uid="{2F1647A4-8C84-E14B-83BA-CB692A19D8A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -1016,7 +1016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1040,8 +1040,11 @@
       <c r="D50" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1052,7 +1055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1063,7 +1066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1074,7 +1077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1085,7 +1088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1096,7 +1099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1107,7 +1110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1118,7 +1121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1131,8 +1134,11 @@
       <c r="D58" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1143,7 +1149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1154,7 +1160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1165,7 +1171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1176,7 +1182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1187,7 +1193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1198,7 +1204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1209,7 +1215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1223,7 +1229,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1234,7 +1240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1245,7 +1251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1256,7 +1262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1267,7 +1273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1278,7 +1284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1289,7 +1295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1300,7 +1306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1313,8 +1319,11 @@
       <c r="D74" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1325,7 +1334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1336,7 +1345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1347,7 +1356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1358,7 +1367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1369,7 +1378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>79</v>
       </c>
@@ -1380,7 +1389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>80</v>
       </c>
@@ -1391,7 +1400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>81</v>
       </c>
@@ -1404,8 +1413,11 @@
       <c r="D82" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>82</v>
       </c>
@@ -1416,7 +1428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>83</v>
       </c>
@@ -1427,7 +1439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>84</v>
       </c>
@@ -1441,7 +1453,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>85</v>
       </c>
@@ -1452,7 +1464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>86</v>
       </c>
@@ -1463,7 +1475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>87</v>
       </c>
@@ -1474,7 +1486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>88</v>
       </c>
@@ -1485,7 +1497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>89</v>
       </c>
@@ -1496,7 +1508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>90</v>
       </c>
@@ -1507,7 +1519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>91</v>
       </c>
@@ -1518,7 +1530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>92</v>
       </c>
@@ -1529,7 +1541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>93</v>
       </c>
@@ -1540,7 +1552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>94</v>
       </c>
@@ -1551,7 +1563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>95</v>
       </c>
